--- a/artfynd/S 4597-2022 artfynd.xlsx
+++ b/artfynd/S 4597-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,35 +788,40 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101204053</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118516672</v>
+        <v>135559252</v>
       </c>
       <c r="B3" t="n">
-        <v>57132</v>
+        <v>4996</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100515</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronspraktbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Buprestis haemorrhoidalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Herbst, 1780</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,31 +829,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sydvästra Lunsen, Upl</t>
+          <t>Lägermossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650120</v>
+        <v>650136</v>
       </c>
       <c r="R3" t="n">
-        <v>6628988</v>
+        <v>6628733</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +882,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grov tallgren på ett hygge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,71 +917,81 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Thomas Persson Vinnersten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Thomas Persson Vinnersten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135559252</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128238648</v>
+        <v>118516672</v>
       </c>
       <c r="B4" t="n">
-        <v>93213</v>
+        <v>57132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Lunsen, Upl</t>
+          <t>Sydvästra Lunsen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650696</v>
+        <v>650120</v>
       </c>
       <c r="R4" t="n">
-        <v>6628139</v>
+        <v>6628988</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +1015,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,81 +1039,79 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118516672</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54122440</v>
+        <v>128238648</v>
       </c>
       <c r="B5" t="n">
-        <v>91930</v>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fredrikslunds herrgård, 2,1 km O-ut, Upl</t>
+          <t>Södra Lunsen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650595</v>
+        <v>650696</v>
       </c>
       <c r="R5" t="n">
-        <v>6628243</v>
+        <v>6628139</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1138,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-04-06</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-04-06</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,98 +1166,75 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Karin Wiklund, Thorleif Joelson, Jörgen Sjöström, Tomas Hallingbäck</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128238648</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84482674</v>
+        <v>54122440</v>
       </c>
       <c r="B6" t="n">
-        <v>26646</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100384</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Franstandad barkskinnbagge</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aradus erosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fallén, 1807</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lunsen, vägslut strax N Tjäreleksbergen, Upl</t>
+          <t>Fredrikslunds herrgård, 2,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650858</v>
+        <v>650595</v>
       </c>
       <c r="R6" t="n">
         <v>6628243</v>
       </c>
       <c r="S6" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,12 +1258,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,72 +1276,113 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Luktticka på grov granstubbe på 15 år gammalt hygge.</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Uppsala-SLU</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Jonsell, Jesper Hansson, Mikael Molander</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Henry Åkerström, Karin Wiklund, Thorleif Joelson, Jörgen Sjöström, Tomas Hallingbäck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54122440</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54241491</v>
+        <v>84482674</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>26646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>100384</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Franstandad barkskinnbagge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Aradus erosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fallén, 1807</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väg vid Tjäderleksbergen, Upl</t>
+          <t>Lunsen, vägslut strax N Tjäreleksbergen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650665</v>
+        <v>650858</v>
       </c>
       <c r="R7" t="n">
-        <v>6628287</v>
+        <v>6628243</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,12 +1406,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-07-07</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-07-07</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,23 +1420,149 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Luktticka på grov granstubbe på 15 år gammalt hygge.</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Uppsala-SLU</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Mats Jonsell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mats Jonsell, Jesper Hansson, Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84482674</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>54241491</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Väg vid Tjäderleksbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>650665</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6628287</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-07-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-07-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Thorleif Joelson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Thorleif Joelson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54241491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 4597-2022 artfynd.xlsx
+++ b/artfynd/S 4597-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118516672</v>
+        <v>135559252</v>
       </c>
       <c r="B3" t="n">
-        <v>57132</v>
+        <v>4996</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100515</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronspraktbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Buprestis haemorrhoidalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Herbst, 1780</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,31 +829,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sydvästra Lunsen, Upl</t>
+          <t>Lägermossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650120</v>
+        <v>650136</v>
       </c>
       <c r="R3" t="n">
-        <v>6628988</v>
+        <v>6628733</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +882,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grov tallgren på ett hygge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,76 +917,81 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Thomas Persson Vinnersten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Thomas Persson Vinnersten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118516672</t>
+          <t>https://artportalen.se/Sighting/135559252</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128238648</v>
+        <v>118516672</v>
       </c>
       <c r="B4" t="n">
-        <v>93213</v>
+        <v>57132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Lunsen, Upl</t>
+          <t>Sydvästra Lunsen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650696</v>
+        <v>650120</v>
       </c>
       <c r="R4" t="n">
-        <v>6628139</v>
+        <v>6628988</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,12 +1015,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,86 +1039,79 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128238648</t>
+          <t>https://artportalen.se/Sighting/118516672</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54122440</v>
+        <v>128238648</v>
       </c>
       <c r="B5" t="n">
-        <v>91930</v>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fredrikslunds herrgård, 2,1 km O-ut, Upl</t>
+          <t>Södra Lunsen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650595</v>
+        <v>650696</v>
       </c>
       <c r="R5" t="n">
-        <v>6628243</v>
+        <v>6628139</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,12 +1138,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-04-06</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-04-06</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,103 +1166,75 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Karin Wiklund, Thorleif Joelson, Jörgen Sjöström, Tomas Hallingbäck</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54122440</t>
+          <t>https://artportalen.se/Sighting/128238648</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84482674</v>
+        <v>54122440</v>
       </c>
       <c r="B6" t="n">
-        <v>26646</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100384</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Franstandad barkskinnbagge</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aradus erosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fallén, 1807</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lunsen, vägslut strax N Tjäreleksbergen, Upl</t>
+          <t>Fredrikslunds herrgård, 2,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650858</v>
+        <v>650595</v>
       </c>
       <c r="R6" t="n">
         <v>6628243</v>
       </c>
       <c r="S6" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,12 +1258,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2015-04-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,77 +1276,113 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Luktticka på grov granstubbe på 15 år gammalt hygge.</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Uppsala-SLU</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Jonsell, Jesper Hansson, Mikael Molander</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Henry Åkerström, Karin Wiklund, Thorleif Joelson, Jörgen Sjöström, Tomas Hallingbäck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84482674</t>
+          <t>https://artportalen.se/Sighting/54122440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54241491</v>
+        <v>84482674</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>26646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>100384</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Franstandad barkskinnbagge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Aradus erosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fallén, 1807</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väg vid Tjäderleksbergen, Upl</t>
+          <t>Lunsen, vägslut strax N Tjäreleksbergen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650665</v>
+        <v>650858</v>
       </c>
       <c r="R7" t="n">
-        <v>6628287</v>
+        <v>6628243</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1380,12 +1406,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-07-07</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-07-07</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,22 +1420,134 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Luktticka på grov granstubbe på 15 år gammalt hygge.</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Uppsala-SLU</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Mats Jonsell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Mats Jonsell, Jesper Hansson, Mikael Molander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84482674</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>54241491</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Väg vid Tjäderleksbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>650665</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6628287</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-07-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-07-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54241491</t>
         </is>
@@ -1423,6 +1561,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4597-2022 artfynd.xlsx
+++ b/artfynd/S 4597-2022 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135559252</v>
       </c>
       <c r="B3" t="n">
-        <v>4996</v>
+        <v>4997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
